--- a/FREVS/other properties.xlsx
+++ b/FREVS/other properties.xlsx
@@ -772,9 +772,9 @@
           <t>Ownership</t>
         </is>
       </c>
-      <c r="B101" s="15">
+      <c r="B101" t="n" s="15">
         <f>B3</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
